--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1395C3BD-6B61-4890-BC1D-56ED2796821D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C404952F-5AB6-404A-A106-0DF290A95501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillBuffProto" sheetId="1" r:id="rId1"/>
@@ -15289,7 +15289,7 @@
         <v>549</v>
       </c>
       <c r="H197" s="6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I197" s="6">
         <v>1</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C404952F-5AB6-404A-A106-0DF290A95501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA7C476-420A-4B77-B6C8-94EE0367AD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2029,10 +2029,6 @@
     <t>Eff_Skill_BaoZha_58</t>
   </si>
   <si>
-    <t>Eff_Skill_ShouLie_2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Eff_Buff_ShiXue</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2106,6 +2102,10 @@
   </si>
   <si>
     <t>巨力震击</t>
+  </si>
+  <si>
+    <t>Eff_Skill_ShouLie_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15426,7 +15426,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="H201" s="6">
         <v>0.1</v>
@@ -15461,7 +15461,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H202" s="6">
         <v>0</v>
@@ -15487,7 +15487,7 @@
         <v>21401010</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E203" s="6">
         <v>1</v>
@@ -15496,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H203" s="6">
         <v>0.5</v>
@@ -15522,7 +15522,7 @@
         <v>21401020</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E204" s="6">
         <v>1</v>
@@ -15531,7 +15531,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H204" s="6">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>21401030</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E205" s="6">
         <v>1</v>
@@ -15566,7 +15566,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H205" s="6">
         <v>0.5</v>
@@ -15592,7 +15592,7 @@
         <v>21401040</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E206" s="6">
         <v>1</v>
@@ -15601,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H206" s="6">
         <v>0.5</v>
@@ -15662,7 +15662,7 @@
         <v>21402010</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E208" s="6">
         <v>1</v>
@@ -15671,7 +15671,7 @@
         <v>0</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H208" s="6">
         <v>0.5</v>
@@ -15697,7 +15697,7 @@
         <v>21402020</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E209" s="6">
         <v>1</v>
@@ -15732,7 +15732,7 @@
         <v>21402030</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E210" s="6">
         <v>1</v>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H210" s="6">
         <v>0</v>
@@ -15767,7 +15767,7 @@
         <v>21402040</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E211" s="6">
         <v>1</v>
@@ -15776,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H211" s="6">
         <v>0</v>
@@ -15802,7 +15802,7 @@
         <v>21403010</v>
       </c>
       <c r="D212" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E212" s="6">
         <v>1</v>
@@ -15837,7 +15837,7 @@
         <v>21403020</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E213" s="6">
         <v>1</v>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H213" s="6">
         <v>0.5</v>
@@ -15872,7 +15872,7 @@
         <v>21403030</v>
       </c>
       <c r="D214" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E214" s="6">
         <v>1</v>
@@ -15881,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H214" s="6">
         <v>0</v>
@@ -15907,7 +15907,7 @@
         <v>21403040</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E215" s="6">
         <v>1</v>
@@ -15916,7 +15916,7 @@
         <v>0</v>
       </c>
       <c r="G215" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H215" s="6">
         <v>0.5</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA7C476-420A-4B77-B6C8-94EE0367AD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4486F05D-DB3E-4EB2-A777-A515E011253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2029,6 +2029,10 @@
     <t>Eff_Skill_BaoZha_58</t>
   </si>
   <si>
+    <t>Eff_Skill_ShouLie_2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Eff_Buff_ShiXue</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2102,10 +2106,6 @@
   </si>
   <si>
     <t>巨力震击</t>
-  </si>
-  <si>
-    <t>Eff_Skill_ShouLie_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15426,7 +15426,7 @@
         <v>0</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="H201" s="6">
         <v>0.1</v>
@@ -15461,7 +15461,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H202" s="6">
         <v>0</v>
@@ -15487,7 +15487,7 @@
         <v>21401010</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E203" s="6">
         <v>1</v>
@@ -15496,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H203" s="6">
         <v>0.5</v>
@@ -15522,7 +15522,7 @@
         <v>21401020</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E204" s="6">
         <v>1</v>
@@ -15531,7 +15531,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H204" s="6">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>21401030</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E205" s="6">
         <v>1</v>
@@ -15566,7 +15566,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H205" s="6">
         <v>0.5</v>
@@ -15592,7 +15592,7 @@
         <v>21401040</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E206" s="6">
         <v>1</v>
@@ -15601,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H206" s="6">
         <v>0.5</v>
@@ -15662,7 +15662,7 @@
         <v>21402010</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E208" s="6">
         <v>1</v>
@@ -15671,7 +15671,7 @@
         <v>0</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H208" s="6">
         <v>0.5</v>
@@ -15697,7 +15697,7 @@
         <v>21402020</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E209" s="6">
         <v>1</v>
@@ -15732,7 +15732,7 @@
         <v>21402030</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E210" s="6">
         <v>1</v>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H210" s="6">
         <v>0</v>
@@ -15767,7 +15767,7 @@
         <v>21402040</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E211" s="6">
         <v>1</v>
@@ -15776,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H211" s="6">
         <v>0</v>
@@ -15802,7 +15802,7 @@
         <v>21403010</v>
       </c>
       <c r="D212" s="18" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E212" s="6">
         <v>1</v>
@@ -15837,7 +15837,7 @@
         <v>21403020</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E213" s="6">
         <v>1</v>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H213" s="6">
         <v>0.5</v>
@@ -15872,7 +15872,7 @@
         <v>21403030</v>
       </c>
       <c r="D214" s="18" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E214" s="6">
         <v>1</v>
@@ -15881,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H214" s="6">
         <v>0</v>
@@ -15907,16 +15907,16 @@
         <v>21403040</v>
       </c>
       <c r="D215" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="E215" s="6">
+        <v>1</v>
+      </c>
+      <c r="F215" s="6">
+        <v>0</v>
+      </c>
+      <c r="G215" s="6" t="s">
         <v>567</v>
-      </c>
-      <c r="E215" s="6">
-        <v>1</v>
-      </c>
-      <c r="F215" s="6">
-        <v>0</v>
-      </c>
-      <c r="G215" s="6" t="s">
-        <v>566</v>
       </c>
       <c r="H215" s="6">
         <v>0.5</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4486F05D-DB3E-4EB2-A777-A515E011253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE609921-96B3-41DC-A0A3-6FAFB26EE2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="2820" windowWidth="21600" windowHeight="11700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillBuffProto" sheetId="1" r:id="rId1"/>
@@ -15569,10 +15569,10 @@
         <v>559</v>
       </c>
       <c r="H205" s="6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I205" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" s="6" t="s">
         <v>31</v>
@@ -15610,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="J206" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K206" s="3">
         <v>0</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE609921-96B3-41DC-A0A3-6FAFB26EE2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60828334-35B6-49ED-8372-864EA87549B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="2820" windowWidth="21600" windowHeight="11700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillBuffProto" sheetId="1" r:id="rId1"/>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60828334-35B6-49ED-8372-864EA87549B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039387DA-7657-4D91-BF26-8AC3DB58DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9161FDF2-DF5D-4FD8-BA19-0D288AEBDBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC75156B-ADC2-4F61-B528-44CDC59E5195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillBuffProto" sheetId="1" r:id="rId1"/>
@@ -2061,10 +2061,6 @@
     <t>Eff_Skill_Status_3</t>
   </si>
   <si>
-    <t>Eff_Skill_XuanFeng</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Eff_Skill_ChongFeng3</t>
   </si>
   <si>
@@ -2110,6 +2106,9 @@
   <si>
     <t>Eff_Skill_Fireball_16</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eff_Skill_XuanFeng_2</t>
   </si>
 </sst>
 </file>
@@ -12105,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H106" s="6">
         <v>0.2</v>
@@ -15526,7 +15525,7 @@
         <v>21401010</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E204" s="6">
         <v>1</v>
@@ -15561,7 +15560,7 @@
         <v>21401020</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E205" s="6">
         <v>1</v>
@@ -15596,7 +15595,7 @@
         <v>21401030</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E206" s="6">
         <v>1</v>
@@ -15631,7 +15630,7 @@
         <v>21401040</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E207" s="6">
         <v>1</v>
@@ -15701,7 +15700,7 @@
         <v>21402010</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E209" s="6">
         <v>1</v>
@@ -15736,7 +15735,7 @@
         <v>21402020</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E210" s="6">
         <v>1</v>
@@ -15771,7 +15770,7 @@
         <v>21402030</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E211" s="6">
         <v>1</v>
@@ -15780,7 +15779,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="H211" s="6">
         <v>0</v>
@@ -15806,7 +15805,7 @@
         <v>21402040</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E212" s="6">
         <v>1</v>
@@ -15841,7 +15840,7 @@
         <v>21403010</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E213" s="6">
         <v>1</v>
@@ -15876,7 +15875,7 @@
         <v>21403020</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E214" s="6">
         <v>1</v>
@@ -15911,7 +15910,7 @@
         <v>21403030</v>
       </c>
       <c r="D215" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E215" s="6">
         <v>1</v>
@@ -15920,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="G215" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H215" s="6">
         <v>0</v>
@@ -15946,7 +15945,7 @@
         <v>21403040</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E216" s="6">
         <v>1</v>
@@ -15955,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H216" s="6">
         <v>0.5</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF018F9-7D4D-4F08-A621-DA4BC0E54B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F341A6-0957-4954-868C-CFB44F7CCDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillBuffProto" sheetId="1" r:id="rId1"/>
@@ -351,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="583">
   <si>
     <t>#</t>
   </si>
@@ -2112,6 +2112,10 @@
   </si>
   <si>
     <t>爆裂击</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eff_Skill_BaoZha_27</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -15748,7 +15752,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>548</v>
+        <v>582</v>
       </c>
       <c r="H210" s="6">
         <v>0.5</v>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F341A6-0957-4954-868C-CFB44F7CCDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321F16D2-565A-4BD0-830B-BD2B96DE5B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14587,7 +14587,7 @@
       <c r="C177" s="6">
         <v>21201040</v>
       </c>
-      <c r="D177" s="20" t="s">
+      <c r="D177" s="6" t="s">
         <v>250</v>
       </c>
       <c r="E177" s="6">

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -1240,7 +1240,7 @@
     <t>疾风标记</t>
   </si>
   <si>
-    <t>Eff_Skill_ShouLie_2</t>
+    <t>Eff_Skill_ShouLie2</t>
   </si>
   <si>
     <t>急速射击</t>
@@ -2105,7 +2105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2317,13 +2317,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
@@ -2341,12 +2334,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2364,7 +2357,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="62">
+  <fills count="55">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2689,48 +2682,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -3043,4224 +2994,4224 @@
     <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="61" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8871,7 +8822,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{1B28627C-A8D0-4EB6-9D02-D35D8964EEF4}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{A20B7129-5EDB-4732-965C-AA9A06CA5720}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
